--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484152_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484152_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.541</v>
+        <v>8.8011</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3798</v>
+        <v>5.668</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1612</v>
+        <v>3.1331</v>
       </c>
       <c r="G2" t="n">
         <v>8.7662</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5126</v>
+        <v>1.7727</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6528</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8597</v>
+        <v>0.8317</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7458</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2547</v>
+        <v>6.2106</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3374</v>
+        <v>4.0969</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9173</v>
+        <v>2.1137</v>
       </c>
       <c r="G3" t="n">
         <v>4.4541</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2772</v>
+        <v>0.6787</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.1361</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3463</v>
+        <v>0.5426</v>
       </c>
       <c r="V3" t="n">
         <v>0.4826</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6738</v>
+        <v>5.2409</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4738</v>
+        <v>2.0689</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.172</v>
       </c>
       <c r="G4" t="n">
         <v>3.5622</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2703</v>
+        <v>0.8374</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3741</v>
+        <v>0.2211</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6444</v>
+        <v>0.6163</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7458</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5388</v>
+        <v>5.2128</v>
       </c>
       <c r="E5" t="n">
-        <v>4.098</v>
+        <v>4.7158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4408</v>
+        <v>0.4969</v>
       </c>
       <c r="G5" t="n">
         <v>5.5128</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1621</v>
+        <v>0.836</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1699</v>
+        <v>0.4479</v>
       </c>
       <c r="U5" t="n">
-        <v>0.332</v>
+        <v>0.3881</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9377</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3813</v>
+        <v>2.9583</v>
       </c>
       <c r="E6" t="n">
-        <v>3.256</v>
+        <v>2.5979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1253</v>
+        <v>0.3604</v>
       </c>
       <c r="G6" t="n">
-        <v>2.158</v>
+        <v>1.6652</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6352</v>
+        <v>0.9372</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7932</v>
+        <v>0.728</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0713</v>
+        <v>2.9866</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5794</v>
+        <v>1.7339</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6507</v>
+        <v>1.2527</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0867</v>
+        <v>-1.3213</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0558</v>
+        <v>-0.7967</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1425</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4261</v>
+        <v>0.6121</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1847</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2414</v>
+        <v>0.6121</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.4826</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0649</v>
+        <v>2.5674</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5923</v>
+        <v>2.6665</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4726</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6652</v>
+        <v>2.158</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9372</v>
+        <v>-0.6352</v>
       </c>
       <c r="I7" t="n">
-        <v>0.728</v>
+        <v>2.7932</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9866</v>
+        <v>2.0713</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7339</v>
+        <v>-0.5794</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2527</v>
+        <v>2.6507</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3213</v>
+        <v>0.0867</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7967</v>
+        <v>-0.0558</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.1425</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7187</v>
+        <v>0.6121</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0056</v>
+        <v>0.5952</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4826</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1206</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5433</v>
+        <v>2.136</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4591</v>
+        <v>1.3603</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0842</v>
+        <v>0.7756</v>
       </c>
       <c r="G8" t="n">
         <v>2.5163</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7691</v>
+        <v>1.3617</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4874</v>
+        <v>0.4138</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2565</v>
+        <v>0.9479</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5437</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9288</v>
+        <v>1.2335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.9028</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1904</v>
+        <v>0.3307</v>
       </c>
       <c r="G9" t="n">
         <v>1.7863</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4166</v>
+        <v>0.7212</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5159</v>
+        <v>0.6802</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0993</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7816</v>
+        <v>-0.3968</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9618</v>
+        <v>1.2906</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7434</v>
+        <v>-1.6873</v>
       </c>
       <c r="G10" t="n">
         <v>1.1627</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2358</v>
+        <v>0.6207</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0794</v>
+        <v>0.4082</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1563</v>
+        <v>0.2125</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9899</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.195</v>
+        <v>-0.4823</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2004</v>
+        <v>0.3721</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9946</v>
+        <v>-0.8544</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2181</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.1488</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.289</v>
+        <v>0.2835</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.275</v>
+        <v>-0.1347</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.239</v>
+        <v>-1.9001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8929</v>
+        <v>-0.6662</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3461</v>
+        <v>-1.2339</v>
       </c>
       <c r="G12" t="n">
         <v>-0.06610000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5203</v>
+        <v>-0.1814</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4988</v>
+        <v>-0.272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0216</v>
+        <v>0.0906</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2558</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>29.711</v>
+        <v>31.58140000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>23.2033</v>
+        <v>25.0736</v>
       </c>
       <c r="F13" t="n">
-        <v>6.507700000000002</v>
+        <v>6.5077</v>
       </c>
       <c r="G13" t="n">
         <v>31.2996</v>
@@ -1468,13 +1468,13 @@
         <v>13.8869</v>
       </c>
       <c r="S13" t="n">
-        <v>6.1498</v>
+        <v>8.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9845</v>
+        <v>3.855</v>
       </c>
       <c r="U13" t="n">
-        <v>4.164999999999999</v>
+        <v>4.165100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-8.730300000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1546</v>
+        <v>1.873</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3925</v>
+        <v>5.6986</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.2379</v>
+        <v>-3.8255</v>
       </c>
       <c r="G14" t="n">
         <v>0.2967</v>
@@ -1546,13 +1546,13 @@
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8166</v>
+        <v>-1.0982</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1732</v>
+        <v>-0.8671</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6434</v>
+        <v>-0.2311</v>
       </c>
       <c r="V14" t="n">
         <v>1.881</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4493</v>
+        <v>-0.2394</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5544</v>
+        <v>-1.9625</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0036</v>
+        <v>1.7231</v>
       </c>
       <c r="G15" t="n">
         <v>-2.0406</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3348</v>
+        <v>0.6461</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6546</v>
+        <v>0.3741</v>
       </c>
       <c r="V15" t="n">
         <v>2.1469</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9815</v>
+        <v>-1.1235</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.2277</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0598</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-1.618</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2398</v>
+        <v>0.0978</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4308</v>
+        <v>0.1247</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.191</v>
+        <v>-0.0269</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,75 +1735,71 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8145</v>
+        <v>-1.6352</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2921</v>
+        <v>-2.1701</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1067</v>
+        <v>0.5349</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5928</v>
+        <v>-2.8794</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-1.9803</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.8991</v>
       </c>
       <c r="J17" t="n">
-        <v>1.794</v>
+        <v>-1.9548</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0686</v>
+        <v>-1.3148</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7255</v>
+        <v>-0.64</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.3868</v>
+        <v>-0.9246</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6638</v>
+        <v>-0.6655</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.723</v>
+        <v>-0.2591</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6394</v>
+        <v>-0.3429</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6803</v>
+        <v>-0.2153</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0409</v>
+        <v>-0.1276</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>G. LOZANO MASSANET</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1813,58 +1809,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2117</v>
+        <v>-2.3365</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5783</v>
+        <v>0.1867</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3666</v>
+        <v>-2.5232</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8794</v>
+        <v>-2.2813</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9803</v>
+        <v>-1.3459</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8991</v>
+        <v>-0.9353</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9548</v>
+        <v>0.181</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3148</v>
+        <v>0.0605</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.64</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9246</v>
+        <v>-2.4622</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6655</v>
+        <v>-1.4064</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2591</v>
+        <v>-1.0558</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9193</v>
+        <v>-0.2537</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2959</v>
+        <v>-0.2594</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1875,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1887,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.971</v>
+        <v>-2.3365</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4299</v>
+        <v>0.1867</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5411</v>
+        <v>-2.5232</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2241</v>
+        <v>-2.2813</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2619</v>
+        <v>-1.3459</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.486</v>
+        <v>-0.9353</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3758</v>
+        <v>0.181</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9355</v>
+        <v>0.0605</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5597</v>
+        <v>0.1205</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5999</v>
+        <v>-2.4622</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6736</v>
+        <v>-1.4064</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9263</v>
+        <v>-1.0558</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5566</v>
+        <v>-0.2537</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0668</v>
+        <v>-0.2594</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,71 +1965,75 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.055</v>
+        <v>-2.5243</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1194</v>
+        <v>0.139</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9356</v>
+        <v>-2.6633</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2813</v>
+        <v>-1.3273</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3459</v>
+        <v>-1.396</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9353</v>
+        <v>0.0687</v>
       </c>
       <c r="J20" t="n">
-        <v>0.181</v>
+        <v>2.2758</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0605</v>
+        <v>0.348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1205</v>
+        <v>1.9278</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4622</v>
+        <v>-3.6031</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4064</v>
+        <v>-1.7441</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0558</v>
+        <v>-1.859</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9721</v>
+        <v>-0.2763</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3004</v>
+        <v>-0.153</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6717</v>
+        <v>-0.1233</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>J. ARNAL DIAZ</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2043,58 +2043,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.055</v>
+        <v>-2.7771</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1194</v>
+        <v>-1.1238</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9356</v>
+        <v>-1.6534</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2813</v>
+        <v>-1.2241</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3459</v>
+        <v>0.2619</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9353</v>
+        <v>-1.486</v>
       </c>
       <c r="J21" t="n">
-        <v>0.181</v>
+        <v>1.3758</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0605</v>
+        <v>1.9355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1205</v>
+        <v>-0.5597</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4622</v>
+        <v>-2.5999</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4064</v>
+        <v>-1.6736</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0558</v>
+        <v>-0.9263</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9721</v>
+        <v>-0.3628</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3004</v>
+        <v>-0.3174</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6717</v>
+        <v>-0.0454</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2087</v>
+        <v>-2.913</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2691</v>
+        <v>-0.8302</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9396</v>
+        <v>-2.0829</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3273</v>
+        <v>-1.5928</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.396</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0687</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2758</v>
+        <v>1.794</v>
       </c>
       <c r="K22" t="n">
-        <v>0.348</v>
+        <v>1.0686</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9278</v>
+        <v>0.7255</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.6031</v>
+        <v>-3.3868</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7441</v>
+        <v>-1.6638</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.859</v>
+        <v>-1.723</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9607</v>
+        <v>-0.4591</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5611</v>
+        <v>-0.442</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3996</v>
+        <v>-0.0171</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,73 +2199,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8259</v>
+        <v>-4.5916</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9416</v>
+        <v>-1.1545</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8843</v>
+        <v>-3.4371</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5447</v>
+        <v>-3.6257</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.343</v>
+        <v>-0.9374</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.2017</v>
+        <v>-2.6883</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.017</v>
+        <v>0.5628</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6585</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6755</v>
+        <v>-0.0325</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.5277</v>
+        <v>-4.1885</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0015</v>
+        <v>-1.5327</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5262</v>
+        <v>-2.6558</v>
       </c>
       <c r="P23" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.1903</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.1903</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.3806</v>
-      </c>
       <c r="S23" t="n">
-        <v>-1.146</v>
+        <v>-0.8984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9408</v>
+        <v>-0.7254</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2053</v>
+        <v>-0.173</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.532</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6544</v>
+        <v>-4.6576</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6647</v>
+        <v>-1.9416</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9897</v>
+        <v>-2.716</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6257</v>
+        <v>-5.5447</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9374</v>
+        <v>-0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6883</v>
+        <v>-5.2017</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5628</v>
+        <v>-1.017</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5953000000000001</v>
+        <v>1.6585</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0325</v>
+        <v>-2.6755</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.1885</v>
+        <v>-4.5277</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5327</v>
+        <v>-2.0015</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6558</v>
+        <v>-2.5262</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9611</v>
+        <v>-0.9777</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2356</v>
+        <v>-0.9408</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7256</v>
+        <v>-0.0369</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="25">
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5922</v>
+        <v>-7.183</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7134</v>
+        <v>-3.0195</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8788</v>
+        <v>-4.1635</v>
       </c>
       <c r="G25" t="n">
         <v>-9.4625</v>
@@ -2400,13 +2400,13 @@
         <v>2.579</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0312</v>
+        <v>-0.6221</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4986</v>
+        <v>-0.8047</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4674</v>
+        <v>0.1827</v>
       </c>
       <c r="V25" t="n">
         <v>4.4886</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.766</v>
+        <v>-30.4447</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.627300000000001</v>
+        <v>-6.2189</v>
       </c>
       <c r="F26" t="n">
-        <v>-26.1389</v>
+        <v>-24.2258</v>
       </c>
       <c r="G26" t="n">
         <v>-33.581</v>
@@ -2451,13 +2451,13 @@
         <v>-15.7045</v>
       </c>
       <c r="J26" t="n">
-        <v>3.831099999999999</v>
+        <v>3.831099999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5695999999999999</v>
+        <v>0.5696000000000003</v>
       </c>
       <c r="L26" t="n">
-        <v>3.2616</v>
+        <v>3.261600000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-37.4119</v>
@@ -2478,13 +2478,13 @@
         <v>13.0934</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.1217</v>
+        <v>-4.801</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.4658</v>
+        <v>-4.0575</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6563</v>
+        <v>-0.7433000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>8.7303</v>
